--- a/public/templates/template-buat-assignment-massal.xlsx
+++ b/public/templates/template-buat-assignment-massal.xlsx
@@ -4,25 +4,58 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Talent" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Assignment" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>nomor_induk</t>
-  </si>
-  <si>
-    <t>NIA-001</t>
-  </si>
-  <si>
-    <t>NIA-002</t>
-  </si>
-  <si>
-    <t>NIA-003</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+  <si>
+    <t>employee_id</t>
+  </si>
+  <si>
+    <t>project_id</t>
+  </si>
+  <si>
+    <t>period_start</t>
+  </si>
+  <si>
+    <t>period_end</t>
+  </si>
+  <si>
+    <t>TAL-0001</t>
+  </si>
+  <si>
+    <t>Project Alpha</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>TAL-0002</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TAL-0003</t>
+  </si>
+  <si>
+    <t>Project Beta</t>
+  </si>
+  <si>
+    <t>2026-02-15</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
   </si>
 </sst>
 </file>
@@ -403,30 +436,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
